--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>인더짐 헬스&amp;요가&amp;필라테스&amp;줌바&amp;PT 서면범내골점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>inthegym02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1340-4096</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>http://pf.kakao.com/_dxaSQxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1086</v>
+        <v>353</v>
       </c>
       <c r="Q2" t="n">
-        <v>817</v>
+        <v>640</v>
       </c>
       <c r="R2" t="n">
-        <v>1903</v>
+        <v>993</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1255567067</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1255567067</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1451</v>
+        <v>1089</v>
       </c>
       <c r="Q3" t="n">
-        <v>1812</v>
+        <v>838</v>
       </c>
       <c r="R3" t="n">
-        <v>3263</v>
+        <v>1927</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>marvelgym_seomyeon@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1373-0898</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marvelgym_seomyeon</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1188</v>
+        <v>631</v>
       </c>
       <c r="Q4" t="n">
-        <v>706</v>
+        <v>489</v>
       </c>
       <c r="R4" t="n">
-        <v>1894</v>
+        <v>1120</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,52 +836,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1732879645</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732879645</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboygym36@naver.com</t>
+          <t>gemstonefitness@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1329-5090</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로 686 2층</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/healthboygym36</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -884,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43d1a</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1295</v>
+        <v>1456</v>
       </c>
       <c r="Q5" t="n">
-        <v>328</v>
+        <v>1825</v>
       </c>
       <c r="R5" t="n">
-        <v>1623</v>
+        <v>3281</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,56 +934,60 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1156400037</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156400037</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>라벨짐 서면점 헬스&amp;PT</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>labelgym_jh@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1343-2263</t>
+          <t>0507-1350-6406</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 신천대로50번길 61 지하1층, 라벨짐</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/labelgym_jh</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -978,13 +1002,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>252</v>
+        <v>4895</v>
       </c>
       <c r="Q6" t="n">
-        <v>888</v>
+        <v>361</v>
       </c>
       <c r="R6" t="n">
-        <v>1140</v>
+        <v>5256</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,51 +1036,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1653633055</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653633055</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>마블피트니스 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>marvelgym_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1373-0898</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://blog.naver.com/marvelgym_seomyeon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1067,15 +1095,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w468mi</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1360</v>
+        <v>1186</v>
       </c>
       <c r="Q7" t="n">
-        <v>785</v>
+        <v>725</v>
       </c>
       <c r="R7" t="n">
-        <v>2145</v>
+        <v>1911</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,51 +1134,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>1732879645</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/1732879645</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1166,10 +1198,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="R8" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,24 +1232,24 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1235,7 +1271,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1260,10 +1296,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1413</v>
+        <v>1436</v>
       </c>
       <c r="Q9" t="n">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="R9" t="n">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1300,41 +1340,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1354,10 +1394,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42pxo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>517</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="R10" t="n">
-        <v>917</v>
+        <v>477</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,51 +1428,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>로마리네필라테스 서면점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>bridgepila1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1497-9057</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 전포대로 204 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://blog.naver.com/bridgepila1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1448,10 +1492,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lhx8</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>270</v>
+        <v>651</v>
       </c>
       <c r="Q11" t="n">
-        <v>886</v>
+        <v>783</v>
       </c>
       <c r="R11" t="n">
-        <v>1156</v>
+        <v>1434</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,957 +1526,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>1080078527</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/1080078527</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>그룹PT 강짐스튜디오 서면점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kang_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1360-8986</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 신천대로62번길 67 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kang.gym_studio/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>585</v>
-      </c>
-      <c r="R12" t="n">
-        <v>843</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1357642240</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1357642240</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>에이치엠피트니스 서면</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>hm_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1473-4456</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 서전로10번길 61 7층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hmfitness_official/</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1666</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>472</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2138</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1175001670</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1175001670</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>리셋 PT 스튜디오</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>sungh0927@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1405-9290</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 부전로 91 동양빌 오피스텔 b1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/sungh0927</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>129</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>847</v>
-      </c>
-      <c r="R14" t="n">
-        <v>976</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1281346464</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1281346464</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>고프로PT 전포점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>kopropt@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1349-3948</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 전포대로209번길 39-8 5층 501호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/kopropt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>92</v>
-      </c>
-      <c r="R15" t="n">
-        <v>234</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1923823040</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1923823040</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>서면PT 온포인트짐 pt&amp;pilates</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>onpointgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1434-0621</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 서전로9번길 18 4층 온포인트짐</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/onpointgym/</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>195</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>925</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1120</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1060194109</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1060194109</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>짐박스피트니스 서면점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1350-6406</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>4951</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>359</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5310</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1895448558</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>크로스핏바로</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>crossfitbaro@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1408-5639</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 중앙대로692번길 38 은아빌딩 지하2층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/crossfitbaro</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>236</v>
-      </c>
-      <c r="R18" t="n">
-        <v>243</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1573964647</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1573964647</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>F45 서면</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>f45centumcity@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1470-0057</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 중앙대로666번길 50 더샵센트럴스타 상가동 지하 2층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://f45korea.com/seomyeon/</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>277</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>131</v>
-      </c>
-      <c r="R19" t="n">
-        <v>408</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1636672798</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1636672798</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>크로스핏 팀케이 피트니스 서면점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4kogc@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 동천로108번길 41 지하1층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/crossfitk</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>147</v>
-      </c>
-      <c r="R20" t="n">
-        <v>175</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1953525039</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1953525039</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>커넥션 하이록스 공식 체육관</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ipalm@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1322-9283</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 서전로37번길 20 지하1층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/connection.hyrox</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>38</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2058921427</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2058921427</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>353</v>
       </c>
       <c r="Q2" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R2" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="R3" t="n">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>gemstonefitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
+          <t>https://talk.naver.com/ct/w43d1a</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>631</v>
+        <v>1458</v>
       </c>
       <c r="Q4" t="n">
-        <v>489</v>
+        <v>1827</v>
       </c>
       <c r="R4" t="n">
-        <v>1120</v>
+        <v>3285</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>0507-1350-6406</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1456</v>
+        <v>4896</v>
       </c>
       <c r="Q5" t="n">
-        <v>1825</v>
+        <v>361</v>
       </c>
       <c r="R5" t="n">
-        <v>3281</v>
+        <v>5257</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,38 +960,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>마블피트니스 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>marvelgym_seomyeon@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-6406</t>
+          <t>0507-1373-0898</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>https://blog.naver.com/marvelgym_seomyeon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
+          <t>https://talk.naver.com/ct/w468mi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4895</v>
+        <v>1190</v>
       </c>
       <c r="Q6" t="n">
-        <v>361</v>
+        <v>728</v>
       </c>
       <c r="R6" t="n">
-        <v>5256</v>
+        <v>1918</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1732879645</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1732879645</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1058,29 +1058,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 서면점</t>
+          <t>우노짐 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marvelgym_seomyeon@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1373-0898</t>
+          <t>0507-1426-0888</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marvelgym_seomyeon</t>
+          <t>https://blog.naver.com/unogym_1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w468mi</t>
+          <t>https://talk.naver.com/ct/w0m3yqq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1186</v>
+        <v>84</v>
       </c>
       <c r="Q7" t="n">
-        <v>725</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
-        <v>1911</v>
+        <v>115</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,51 +1134,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1732879645</t>
+          <t>2026422991</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732879645</t>
+          <t>https://m.place.naver.com/place/2026422991</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cocoagymbn@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1374-1945</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 181 지하1층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocoagymbn</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whhuq4g</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53</v>
+        <v>1441</v>
       </c>
       <c r="Q8" t="n">
-        <v>103</v>
+        <v>1056</v>
       </c>
       <c r="R8" t="n">
-        <v>156</v>
+        <v>2497</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2057373274</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057373274</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1296,14 +1296,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1315,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1436</v>
+        <v>728</v>
       </c>
       <c r="Q9" t="n">
-        <v>1054</v>
+        <v>492</v>
       </c>
       <c r="R9" t="n">
-        <v>2490</v>
+        <v>1220</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1438,105 +1434,203 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>로마리네필라테스 서면점</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bridgepila1@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1497-9057</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/motionuppt2879</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsi0guq</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>708</v>
+      </c>
+      <c r="R11" t="n">
+        <v>939</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1594058930</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594058930</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>로마리네필라테스 서면점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bridgepila1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1497-9057</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>부산 부산진구 전포대로 204 201호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/bridgepila1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4lhx8</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>651</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>783</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1434</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>787</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1439</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1080078527</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1080078527</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1458</v>
+        <v>632</v>
       </c>
       <c r="Q4" t="n">
-        <v>1827</v>
+        <v>489</v>
       </c>
       <c r="R4" t="n">
-        <v>3285</v>
+        <v>1121</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,38 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>gemstonefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1350-6406</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -909,12 +905,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
+          <t>https://talk.naver.com/ct/w43d1a</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -923,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4896</v>
+        <v>1458</v>
       </c>
       <c r="Q5" t="n">
-        <v>361</v>
+        <v>1827</v>
       </c>
       <c r="R5" t="n">
-        <v>5257</v>
+        <v>3285</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -960,34 +956,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 서면점</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marvelgym_seomyeon@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1373-0898</t>
+          <t>0507-1350-6406</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marvelgym_seomyeon</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w468mi</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1190</v>
+        <v>4896</v>
       </c>
       <c r="Q6" t="n">
-        <v>728</v>
+        <v>361</v>
       </c>
       <c r="R6" t="n">
-        <v>1918</v>
+        <v>5257</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1732879645</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732879645</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1058,29 +1058,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>마블피트니스 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>marvelgym_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1373-0898</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://blog.naver.com/marvelgym_seomyeon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0m3yqq</t>
+          <t>https://talk.naver.com/ct/w468mi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>84</v>
+        <v>1190</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>728</v>
       </c>
       <c r="R7" t="n">
-        <v>115</v>
+        <v>1918</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1732879645</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1732879645</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1151,34 +1151,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>우노짐 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1426-0888</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/unogym_1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w0m3yqq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1441</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1056</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
-        <v>2497</v>
+        <v>115</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>2026422991</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/2026422991</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1254,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬짐 HELL GYM</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hellgymseomyeon@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1435-7378</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgymseomyeon</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1296,10 +1296,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>728</v>
+        <v>1441</v>
       </c>
       <c r="Q9" t="n">
-        <v>492</v>
+        <v>1056</v>
       </c>
       <c r="R9" t="n">
-        <v>1220</v>
+        <v>2497</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1847755059</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847755059</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1441,34 +1445,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>로마리네필라테스 서면점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>bridgepila1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1497-9057</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 전포대로 204 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>https://blog.naver.com/bridgepila1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
+          <t>https://talk.naver.com/ct/w4lhx8</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>231</v>
+        <v>652</v>
       </c>
       <c r="Q11" t="n">
-        <v>708</v>
+        <v>787</v>
       </c>
       <c r="R11" t="n">
-        <v>939</v>
+        <v>1439</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1526,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>1080078527</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/1080078527</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>로마리네필라테스 서면점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bridgepila1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1497-9057</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산 부산진구 전포대로 204 201호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bridgepila1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lhx8</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>652</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>787</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1439</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1080078527</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1080078527</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="Q3" t="n">
         <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -977,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1002,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1075,7 +1055,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산광역시 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1100,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w468mi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1119,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="Q7" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="R7" t="n">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1173,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산광역시 부산진구 부전로 94 영동프라자 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1198,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0m3yqq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1271,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1296,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,7 +1337,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1394,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1416,10 +1380,10 @@
         <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R10" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1445,96 +1409,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>로마리네필라테스 서면점</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bridgepila1@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1497-9057</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>부산광역시 부산진구 전포대로 207 3층 모션업PT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/motionuppt2879</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>708</v>
+      </c>
+      <c r="R11" t="n">
+        <v>939</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1594058930</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594058930</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>로마리네필라테스 서면점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bridgepila1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1497-9057</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>부산 부산진구 전포대로 204 201호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/bridgepila1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4lhx8</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>652</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>787</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1439</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1080078527</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1080078527</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -426,13 +426,13 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1094</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>847</v>
+        <v>489</v>
       </c>
       <c r="R3" t="n">
-        <v>1941</v>
+        <v>1121</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,18 +797,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>632</v>
+        <v>1093</v>
       </c>
       <c r="Q4" t="n">
-        <v>489</v>
+        <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>1121</v>
+        <v>1940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43d1a</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +977,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +1002,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1055,7 +1075,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1100,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w468mi</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="Q7" t="n">
         <v>729</v>
       </c>
       <c r="R7" t="n">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1127,34 +1151,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1198,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>84</v>
+        <v>1441</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>1056</v>
       </c>
       <c r="R8" t="n">
-        <v>115</v>
+        <v>2497</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1232,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,15 +1291,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42pxo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1441</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>1056</v>
+        <v>321</v>
       </c>
       <c r="R9" t="n">
-        <v>2497</v>
+        <v>478</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1352,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/motionuppt2879</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,15 +1389,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsi0guq</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="n">
-        <v>321</v>
+        <v>708</v>
       </c>
       <c r="R10" t="n">
-        <v>478</v>
+        <v>939</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1594058930</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1594058930</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1450,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>뉴짐스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>newgyms@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1313-2236</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>https://www.instagram.com/n.gyms_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,15 +1487,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w438s8</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>231</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="n">
-        <v>708</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>939</v>
+        <v>126</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1526,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>1810951830</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>632</v>
+        <v>1093</v>
       </c>
       <c r="Q3" t="n">
-        <v>489</v>
+        <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>1121</v>
+        <v>1940</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gemstonefitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w43d1a</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1093</v>
+        <v>1458</v>
       </c>
       <c r="Q4" t="n">
-        <v>847</v>
+        <v>1827</v>
       </c>
       <c r="R4" t="n">
-        <v>1940</v>
+        <v>3285</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>0507-1350-6406</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1458</v>
+        <v>4896</v>
       </c>
       <c r="Q5" t="n">
-        <v>1827</v>
+        <v>361</v>
       </c>
       <c r="R5" t="n">
-        <v>3285</v>
+        <v>5257</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,48 +960,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>마블피트니스 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>marvelgym_seomyeon@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-6406</t>
+          <t>0507-1373-0898</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
+          <t>https://talk.naver.com/ct/w468mi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4896</v>
+        <v>1195</v>
       </c>
       <c r="Q6" t="n">
-        <v>361</v>
+        <v>729</v>
       </c>
       <c r="R6" t="n">
-        <v>5257</v>
+        <v>1924</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,51 +1036,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1732879645</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1732879645</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 서면점</t>
+          <t>라벨짐 전포점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marvelgym_seomyeon@naver.com</t>
+          <t>labelgym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1373-0898</t>
+          <t>0507-1473-2259</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산 부산진구 동성로 136 4층 401호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marvelgym_seomyeon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w468mi</t>
+          <t>https://talk.naver.com/ct/w4dago</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1194</v>
+        <v>223</v>
       </c>
       <c r="Q7" t="n">
-        <v>729</v>
+        <v>319</v>
       </c>
       <c r="R7" t="n">
-        <v>1923</v>
+        <v>542</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1732879645</t>
+          <t>1949510224</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732879645</t>
+          <t>https://m.place.naver.com/place/1949510224</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1156,29 +1156,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>스마일짐 PT 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>dntnals421@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1318-0661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서면로 51 10층 1001호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,24 +1188,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1441</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1056</v>
+        <v>60</v>
       </c>
       <c r="R8" t="n">
-        <v>2497</v>
+        <v>98</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1855077210</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1855077210</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1291,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>1441</v>
       </c>
       <c r="Q9" t="n">
-        <v>321</v>
+        <v>1056</v>
       </c>
       <c r="R9" t="n">
-        <v>478</v>
+        <v>2497</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1389,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1399,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>708</v>
+        <v>321</v>
       </c>
       <c r="R10" t="n">
-        <v>939</v>
+        <v>478</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1450,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.gyms_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1482,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1497,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
+          <t>https://talk.naver.com/ct/wsi0guq</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1511,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>231</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>708</v>
       </c>
       <c r="R11" t="n">
-        <v>126</v>
+        <v>939</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>1594058930</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/1594058930</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>로마리네필라테스 서면점</t>
+          <t>뉴짐스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bridgepila1@naver.com</t>
+          <t>newgyms@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1497-9057</t>
+          <t>0507-1313-2236</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 204 201호</t>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bridgepila1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1580,12 +1576,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1595,7 +1591,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4lhx8</t>
+          <t>https://talk.naver.com/ct/w438s8</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1609,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>652</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="n">
-        <v>787</v>
+        <v>60</v>
       </c>
       <c r="R12" t="n">
-        <v>1439</v>
+        <v>126</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1624,17 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1080078527</t>
+          <t>1810951830</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080078527</t>
+          <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -679,12 +675,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1458</v>
+        <v>632</v>
       </c>
       <c r="Q4" t="n">
-        <v>1827</v>
+        <v>489</v>
       </c>
       <c r="R4" t="n">
-        <v>3285</v>
+        <v>1121</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,38 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>gemstonefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1350-6406</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -904,17 +888,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -923,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4896</v>
+        <v>1458</v>
       </c>
       <c r="Q5" t="n">
-        <v>361</v>
+        <v>1827</v>
       </c>
       <c r="R5" t="n">
-        <v>5257</v>
+        <v>3285</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -960,59 +940,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 서면점</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marvelgym_seomyeon@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1373-0898</t>
+          <t>0507-1350-6406</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w468mi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1195</v>
+        <v>4896</v>
       </c>
       <c r="Q6" t="n">
-        <v>729</v>
+        <v>361</v>
       </c>
       <c r="R6" t="n">
-        <v>1924</v>
+        <v>5257</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1732879645</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732879645</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1053,34 +1033,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>라벨짐 전포점 헬스&amp;PT</t>
+          <t>마블피트니스 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>labelgym2@naver.com</t>
+          <t>marvelgym_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1473-2259</t>
+          <t>0507-1373-0898</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 동성로 136 4층 401호</t>
+          <t>부산광역시 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/marvelgym_seomyeon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1090,24 +1070,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dago</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1119,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>223</v>
+        <v>1196</v>
       </c>
       <c r="Q7" t="n">
-        <v>319</v>
+        <v>729</v>
       </c>
       <c r="R7" t="n">
-        <v>542</v>
+        <v>1925</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1949510224</t>
+          <t>1732879645</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949510224</t>
+          <t>https://m.place.naver.com/place/1732879645</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1156,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스마일짐 PT 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dntnals421@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1318-0661</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 51 10층 1001호</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,12 +1164,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>1441</v>
       </c>
       <c r="Q8" t="n">
-        <v>60</v>
+        <v>1055</v>
       </c>
       <c r="R8" t="n">
-        <v>98</v>
+        <v>2496</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,407 +1204,15 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1855077210</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855077210</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>멋짐 서면점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>mutgym8689@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1314-8689</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/mutgym8689</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1441</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1056</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2497</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1024587035</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>아르케 핏 PT 서면전포점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>zon_t@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1345-6738</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>157</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>321</v>
-      </c>
-      <c r="R10" t="n">
-        <v>478</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1578556277</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>모션업PT 전포 6호점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>motionuppt2879@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1487-7556</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>231</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>708</v>
-      </c>
-      <c r="R11" t="n">
-        <v>939</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1594058930</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>뉴짐스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>newgyms@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1313-2236</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>60</v>
-      </c>
-      <c r="R12" t="n">
-        <v>126</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1810951830</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q2" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="R2" t="n">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1093</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>847</v>
+        <v>489</v>
       </c>
       <c r="R3" t="n">
-        <v>1940</v>
+        <v>1121</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,18 +797,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>632</v>
+        <v>1093</v>
       </c>
       <c r="Q4" t="n">
-        <v>489</v>
+        <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>1121</v>
+        <v>1940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43d1a</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +977,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +1002,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1001,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4896</v>
+        <v>4898</v>
       </c>
       <c r="Q6" t="n">
         <v>361</v>
       </c>
       <c r="R6" t="n">
-        <v>5257</v>
+        <v>5259</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,34 +1058,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 서면점</t>
+          <t>헬스보이짐 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marvelgym_seomyeon@naver.com</t>
+          <t>healthboygym36@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1373-0898</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로 25 이오스프라자 6층 601호, 602호</t>
+          <t>부산 부산진구 중앙대로 686 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marvelgym_seomyeon</t>
+          <t>https://link.inpock.co.kr/healthboygym36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gsu5</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1196</v>
+        <v>1296</v>
       </c>
       <c r="Q7" t="n">
-        <v>729</v>
+        <v>338</v>
       </c>
       <c r="R7" t="n">
-        <v>1925</v>
+        <v>1634</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1732879645</t>
+          <t>1156400037</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732879645</t>
+          <t>https://m.place.naver.com/place/1156400037</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,92 +1147,582 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>https://blog.naver.com/cocoagymbn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>103</v>
+      </c>
+      <c r="R8" t="n">
+        <v>156</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2057373274</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2057373274</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>우노짐 헬스&amp;PT 서면점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unogym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1426-0888</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/unogym_1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0m3yqq</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>31</v>
+      </c>
+      <c r="R9" t="n">
+        <v>115</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026422991</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2026422991</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>스마일짐 PT 서면점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>wns8gh88@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1318-0661</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>부산 부산진구 서면로 51 10층 1001호</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/smilegym_pt?igsh=NzhvNDEweWRhNDg4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>59</v>
+      </c>
+      <c r="R10" t="n">
+        <v>97</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1855077210</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1855077210</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>멋짐 서면점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mutgym8689@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1314-8689</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1441</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1055</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2496</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1442</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1056</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2498</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1024587035</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>아르케 핏 PT 서면전포점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>zon_t@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1345-6738</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/arkhe_fit</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42pxo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>322</v>
+      </c>
+      <c r="R12" t="n">
+        <v>479</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1578556277</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1578556277</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>로마리네필라테스 서면점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bridgepila1@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1497-9057</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>부산 부산진구 전포대로 204 201호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bridgepila1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lhx8</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>790</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1442</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1080078527</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1080078527</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q2" t="n">
         <v>642</v>
       </c>
       <c r="R2" t="n">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,22 +695,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>632</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>489</v>
+        <v>848</v>
       </c>
       <c r="R3" t="n">
-        <v>1121</v>
+        <v>1940</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gemstonefitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,22 +789,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1093</v>
+        <v>1459</v>
       </c>
       <c r="Q4" t="n">
-        <v>847</v>
+        <v>1828</v>
       </c>
       <c r="R4" t="n">
-        <v>1940</v>
+        <v>3287</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,34 +846,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>0507-1350-6406</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -900,17 +892,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1458</v>
+        <v>4898</v>
       </c>
       <c r="Q5" t="n">
-        <v>1827</v>
+        <v>361</v>
       </c>
       <c r="R5" t="n">
-        <v>3285</v>
+        <v>5259</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -956,33 +944,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>헬스보이짐 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1350-6406</t>
-        </is>
-      </c>
+          <t>healthboygym36@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산광역시 부산진구 중앙대로 686 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>https://link.inpock.co.kr/healthboygym36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1002,17 +982,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4898</v>
+        <v>1296</v>
       </c>
       <c r="Q6" t="n">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="R6" t="n">
-        <v>5259</v>
+        <v>1634</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1156400037</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1156400037</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1058,30 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 서면점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym36@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1374-1945</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 686 2층</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/healthboygym36</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1081,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4gsu5</t>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1296</v>
+        <v>53</v>
       </c>
       <c r="Q7" t="n">
-        <v>338</v>
+        <v>103</v>
       </c>
       <c r="R7" t="n">
-        <v>1634</v>
+        <v>156</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1156400037</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156400037</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
+          <t>스마일짐 PT 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cocoagymbn@naver.com</t>
+          <t>wns8gh88@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1374-1945</t>
+          <t>0507-1318-0661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 181 지하1층</t>
+          <t>부산 부산진구 서면로 51 10층 1001호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocoagymbn</t>
+          <t>https://www.instagram.com/smilegym_pt?igsh=NzhvNDEweWRhNDg4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,19 +1169,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whhuq4g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="R8" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2057373274</t>
+          <t>1855077210</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057373274</t>
+          <t>https://m.place.naver.com/place/1855077210</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0m3yqq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>84</v>
+        <v>1445</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>1056</v>
       </c>
       <c r="R9" t="n">
-        <v>115</v>
+        <v>2501</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스마일짐 PT 서면점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wns8gh88@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1318-0661</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 51 10층 1001호</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/smilegym_pt?igsh=NzhvNDEweWRhNDg4</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1405,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>38</v>
+        <v>729</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>492</v>
       </c>
       <c r="R10" t="n">
-        <v>97</v>
+        <v>1221</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1855077210</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855077210</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1461,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1442</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>1056</v>
+        <v>322</v>
       </c>
       <c r="R11" t="n">
-        <v>2498</v>
+        <v>479</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,51 +1490,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>로마리네필라테스 서면점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>bridgepila1@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1497-9057</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 전포대로 204 201호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/bridgepila1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1577,7 +1549,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1559,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/w4lhx8</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1573,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>157</v>
+        <v>652</v>
       </c>
       <c r="Q12" t="n">
-        <v>322</v>
+        <v>790</v>
       </c>
       <c r="R12" t="n">
-        <v>479</v>
+        <v>1442</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,115 +1588,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1080078527</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1080078527</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>로마리네필라테스 서면점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>bridgepila1@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1497-9057</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산 부산진구 전포대로 204 201호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bridgepila1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lhx8</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>652</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>790</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1442</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1080078527</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1080078527</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -624,10 +628,10 @@
         <v>355</v>
       </c>
       <c r="Q2" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="R2" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>848</v>
+        <v>490</v>
       </c>
       <c r="R3" t="n">
-        <v>1940</v>
+        <v>1122</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,18 +797,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1459</v>
+        <v>1092</v>
       </c>
       <c r="Q4" t="n">
-        <v>1828</v>
+        <v>849</v>
       </c>
       <c r="R4" t="n">
-        <v>3287</v>
+        <v>1941</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,38 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>gemstonefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1350-6406</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -892,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43d1a</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4898</v>
+        <v>1459</v>
       </c>
       <c r="Q5" t="n">
-        <v>361</v>
+        <v>1831</v>
       </c>
       <c r="R5" t="n">
-        <v>5259</v>
+        <v>3290</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,25 +956,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 서면점</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym36@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1350-6406</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로 686 2층</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/healthboygym36</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,13 +1002,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1296</v>
+        <v>4898</v>
       </c>
       <c r="Q6" t="n">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="R6" t="n">
-        <v>1634</v>
+        <v>5259</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1036,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1156400037</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156400037</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1058,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
+          <t>헬스보이짐 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cocoagymbn@naver.com</t>
+          <t>healthboygym36@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1374-1945</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 181 지하1층</t>
+          <t>부산 부산진구 중앙대로 686 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocoagymbn</t>
+          <t>https://link.inpock.co.kr/healthboygym36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1081,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whhuq4g</t>
+          <t>https://talk.naver.com/ct/w4gsu5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>53</v>
+        <v>1296</v>
       </c>
       <c r="Q7" t="n">
-        <v>103</v>
+        <v>339</v>
       </c>
       <c r="R7" t="n">
-        <v>156</v>
+        <v>1635</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2057373274</t>
+          <t>1156400037</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057373274</t>
+          <t>https://m.place.naver.com/place/1156400037</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스마일짐 PT 서면점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wns8gh88@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1318-0661</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 51 10층 1001호</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/smilegym_pt?igsh=NzhvNDEweWRhNDg4</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="R8" t="n">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1855077210</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855077210</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>스마일짐 PT 서면점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>wns8gh88@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1318-0661</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서면로 51 10층 1001호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/smilegym_pt?igsh=NzhvNDEweWRhNDg4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1445</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
-        <v>1056</v>
+        <v>57</v>
       </c>
       <c r="R9" t="n">
-        <v>2501</v>
+        <v>94</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1855077210</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1855077210</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬짐 HELL GYM</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hellgymseomyeon@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1435-7378</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgymseomyeon</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>729</v>
+        <v>1446</v>
       </c>
       <c r="Q10" t="n">
-        <v>492</v>
+        <v>1057</v>
       </c>
       <c r="R10" t="n">
-        <v>1221</v>
+        <v>2503</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1847755059</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847755059</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>로마리네필라테스 서면점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>bridgepila1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1497-9057</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 전포대로 204 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/bridgepila1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1461,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/w4lhx8</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1475,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>652</v>
       </c>
       <c r="Q11" t="n">
-        <v>322</v>
+        <v>791</v>
       </c>
       <c r="R11" t="n">
-        <v>479</v>
+        <v>1443</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,113 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1080078527</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1080078527</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>로마리네필라테스 서면점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bridgepila1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1497-9057</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산 부산진구 전포대로 204 201호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bridgepila1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lhx8</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>652</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>790</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1442</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1080078527</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1080078527</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q2" t="n">
         <v>643</v>
       </c>
       <c r="R2" t="n">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>632</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>490</v>
+        <v>849</v>
       </c>
       <c r="R3" t="n">
-        <v>1122</v>
+        <v>1941</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1092</v>
+        <v>1448</v>
       </c>
       <c r="Q4" t="n">
-        <v>849</v>
+        <v>1057</v>
       </c>
       <c r="R4" t="n">
-        <v>1941</v>
+        <v>2505</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
         <v>1459</v>
       </c>
       <c r="Q5" t="n">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="R5" t="n">
-        <v>3290</v>
+        <v>3292</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,14 +1386,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1446</v>
+        <v>729</v>
       </c>
       <c r="Q10" t="n">
-        <v>1057</v>
+        <v>493</v>
       </c>
       <c r="R10" t="n">
-        <v>2503</v>
+        <v>1222</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_헬스장.xlsx
+++ b/naver-place-crawler/results_health/서면_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1448</v>
+        <v>632</v>
       </c>
       <c r="Q4" t="n">
-        <v>1057</v>
+        <v>490</v>
       </c>
       <c r="R4" t="n">
-        <v>2505</v>
+        <v>1122</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gemstonefitness@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-5090</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemstonefitness</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43d1a</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1459</v>
+        <v>1448</v>
       </c>
       <c r="Q5" t="n">
-        <v>1833</v>
+        <v>1057</v>
       </c>
       <c r="R5" t="n">
-        <v>3292</v>
+        <v>2505</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1994781671</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994781671</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,38 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 서면점</t>
+          <t>젬스톤피트니스 서면점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>gemstonefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-6406</t>
+          <t>0507-1329-5090</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
+          <t>부산 부산진구 동천로 112 3층 젬스톤피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=43</t>
+          <t>https://blog.naver.com/gemstonefitness</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1007,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
+          <t>https://talk.naver.com/ct/w43d1a</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4898</v>
+        <v>1459</v>
       </c>
       <c r="Q6" t="n">
-        <v>361</v>
+        <v>1833</v>
       </c>
       <c r="R6" t="n">
-        <v>5259</v>
+        <v>3292</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1895448558</t>
+          <t>1994781671</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895448558</t>
+          <t>https://m.place.naver.com/place/1994781671</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1058,25 +1054,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 서면점</t>
+          <t>짐박스피트니스 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym36@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1350-6406</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로 686 2층</t>
+          <t>부산 부산진구 중앙대로 704 동보프라자 B1호, B2호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/healthboygym36</t>
+          <t>https://gymboxx.com/onceinayear?gym=43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,12 +1105,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4gsu5</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1296</v>
+        <v>4898</v>
       </c>
       <c r="Q7" t="n">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="R7" t="n">
-        <v>1635</v>
+        <v>5259</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1134,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1156400037</t>
+          <t>1895448558</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156400037</t>
+          <t>https://m.place.naver.com/place/1895448558</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,34 +1156,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
+          <t>헬스보이짐 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cocoagymbn@naver.com</t>
+          <t>healthboygym36@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1374-1945</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 181 지하1층</t>
+          <t>부산 부산진구 중앙대로 686 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocoagymbn</t>
+          <t>https://link.inpock.co.kr/healthboygym36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whhuq4g</t>
+          <t>https://talk.naver.com/ct/w4gsu5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53</v>
+        <v>1296</v>
       </c>
       <c r="Q8" t="n">
-        <v>103</v>
+        <v>339</v>
       </c>
       <c r="R8" t="n">
-        <v>156</v>
+        <v>1635</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2057373274</t>
+          <t>1156400037</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057373274</t>
+          <t>https://m.place.naver.com/place/1156400037</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스마일짐 PT 서면점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wns8gh88@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1318-0661</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 51 10층 1001호</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/smilegym_pt?igsh=NzhvNDEweWRhNDg4</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="R9" t="n">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1855077210</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855077210</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
